--- a/assets/constructions/examples/ctd_jfe_m.xlsx
+++ b/assets/constructions/examples/ctd_jfe_m.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,29 +634,58 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TAP M 4x0,7 S 80 N  6GX TiN</t>
+          <t>ET138-FJN-050080E-RH7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VERGNANO</t>
+          <t>GESAC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S80N6GXTiN</t>
+          <t>ET138-FJN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PMNS</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>M60</t>
@@ -669,53 +698,45 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6GX</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M5x0.8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.7</v>
+        <v>4.65</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>5</v>
-      </c>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>6</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>18</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>70</v>
+        <v>63.5</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -730,7 +751,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:6X4.9</t>
+          <t>DCON_X_DRVS:5.5x4.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -739,26 +760,22 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>TiN</t>
+          <t>AlCrN</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>HSSK</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>HSSK</t>
-        </is>
-      </c>
+          <t>HSS-E</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -770,47 +787,66 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>DIN 371</t>
+          <t>JIS</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="b">
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="AN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>2025 / GESAC Инструменты для сверления отверстий</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
         <v>1</v>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>BOTH</t>
-        </is>
-      </c>
-      <c r="AN2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>2020 / Vergnano Catalog</t>
+      <c r="AQ2" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AS2" t="n">
+        <v>1152.55</v>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>PM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TAP M 12x1,5 P 901 N "E" RED-MAXX</t>
+          <t>ET166-FJN-014030E-RH4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VERGNANO</t>
+          <t>GESAC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P901 NE</t>
+          <t>ET166-FJN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PMNS</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -821,32 +857,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Coarse</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6HX</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>M12x1,5</t>
+          <t>M1.4x0.3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>11.3</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -855,24 +891,18 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>h9</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>15</v>
-      </c>
-      <c r="T3" t="n">
-        <v>15</v>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -887,7 +917,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:9X7</t>
+          <t>DCON_X_DRVS:3x2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -896,14 +926,18 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>RED-MAXX</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+          <t>DLC</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>HSS-E</t>
+        </is>
+      </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
@@ -919,7 +953,7 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>DIN 2174</t>
+          <t>JIS</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
@@ -929,37 +963,56 @@
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>BLIND</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="AN3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2025 / GESAC Инструменты для сверления отверстий</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
         <v>1</v>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>2022 / Vergnano-Thread-Mills</t>
+      <c r="AQ3" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AS3" t="n">
+        <v>708.25</v>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TAP M 8x1,25 BP 80 N R TIN</t>
+          <t>FAS481VS-3 M14 6HX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VERGNANO</t>
+          <t>DC SWISS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BP80NRTiN</t>
+          <t>FAS481VS-3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMNS</t>
+          <t>PMKNSH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -979,23 +1032,23 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M14x2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.4</v>
+        <v>13.1</v>
       </c>
       <c r="M4" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
@@ -1004,24 +1057,20 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>h9</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="T4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U4" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
@@ -1036,7 +1085,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:8X6.2</t>
+          <t>DCON_X_DRVS:11x9</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1045,26 +1094,22 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>TiN</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>HSSK</t>
-        </is>
-      </c>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>HSSK</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1076,14 +1121,14 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>DIN 376</t>
+          <t>DIN 2189</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="b">
-        <v>1</v>
-      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
           <t>BOTH</t>
@@ -1094,24 +1139,35 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2020 / Vergnano Catalog</t>
+          <t>2020 / DC Swiss website</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6722TF-M1.4</t>
+          <t>TAP M 4x0,7 A 80  TICN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ILIX</t>
+          <t>VERGNANO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6722TF</t>
+          <t>A80TiCN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1119,11 +1175,7 @@
           <t>PN</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>M60</t>
@@ -1140,23 +1192,23 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>M1,4</t>
+          <t>M4x0.7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -1164,9 +1216,11 @@
           <t>C</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1174,13 +1228,13 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="U5" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1195,7 +1249,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:2.5X2.1</t>
+          <t>DCON_X_DRVS:4.5x3.4</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1204,21 +1258,21 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>TiALN FUTURA</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>HSS-CO</t>
+          <t>HSSE</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>HSS-CO</t>
+          <t>HSSE</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1235,34 +1289,43 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>DIN 371</t>
+          <t>DIN 2174</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="n">
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
         <v>0</v>
       </c>
-      <c r="AL5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>BOTH</t>
-        </is>
-      </c>
-      <c r="AN5" t="b">
-        <v>1</v>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2019/ilix_katalog_taps.pdf</t>
+          <t>2020 / Vergnano Catalog</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>PN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FAS381VS-3 M6x0.75 6HX</t>
+          <t>FAS581VS-3 M3 6HX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1272,7 +1335,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FAS381VS-3</t>
+          <t>FAS581VS-3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1288,7 +1351,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Coarse</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1297,23 +1360,23 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>M6x0,75</t>
+          <t>M3x0.5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -1322,26 +1385,26 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="U6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1350,7 +1413,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:6X4.9</t>
+          <t>DCON_X_DRVS:3.5x2.7</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1359,7 +1422,7 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1384,11 +1447,7 @@
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>DIN 2184-1</t>
-        </is>
-      </c>
+      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1405,6 +1464,17 @@
       <c r="AO6" t="inlineStr">
         <is>
           <t>2020 / DC Swiss website</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
